--- a/artfynd/A 53915-2024 artfynd.xlsx
+++ b/artfynd/A 53915-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121795069</v>
+        <v>121800389</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -721,17 +727,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svaltorpsmossarna, Svaltorpsmossarna, Dls</t>
+          <t>Svaltorpsmossarna, Grönhult, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>348184</v>
+        <v>348178</v>
       </c>
       <c r="R2" t="n">
-        <v>6519712</v>
+        <v>6519779</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,11 +767,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska födosökspår sannolikt skapade inom 5 år tillbaks.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,24 +783,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrskog med en hel del gran men även tall på frisk- frisk-fuktig och fuktig mark. Förekomst av stående död ved.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -954,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121800389</v>
+        <v>121795069</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,16 +956,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -987,16 +973,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1006,17 +988,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svaltorpsmossarna, Grönhult, Dls</t>
+          <t>Svaltorpsmossarna, Svaltorpsmossarna, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>348178</v>
+        <v>348184</v>
       </c>
       <c r="R4" t="n">
-        <v>6519779</v>
+        <v>6519712</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1046,6 +1028,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska födosökspår från basen och flera meter upp på en stående död granstam. Relativt små uthackade hål genom barken och in till veden. Sannolikt skapade inom 1-2 år tillbaks. Fyndplatsen finns ca 600-700 meter väster om Rannebergets naturreservat där det lever tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,9 +1049,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrskog med en hel del gran men även tall på frisk- frisk-fuktig och fuktig mark. Förekomst av stående död ved.</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 53915-2024 artfynd.xlsx
+++ b/artfynd/A 53915-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121800389</v>
+        <v>121794687</v>
       </c>
       <c r="B2" t="n">
         <v>57373</v>
@@ -708,16 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -727,17 +721,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svaltorpsmossarna, Grönhult, Dls</t>
+          <t>Svaltorpsmossarna, Svaltorpsmossarna, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>348178</v>
+        <v>348195</v>
       </c>
       <c r="R2" t="n">
-        <v>6519779</v>
+        <v>6519676</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -783,9 +777,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog med en hel del gran men även tall på frisk- frisk-fuktig och fuktig mark. Förekomst av stående död ved.</t>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -803,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121794687</v>
+        <v>121800389</v>
       </c>
       <c r="B3" t="n">
         <v>57373</v>
@@ -836,10 +845,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -849,17 +864,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svaltorpsmossarna, Svaltorpsmossarna, Dls</t>
+          <t>Svaltorpsmossarna, Grönhult, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>348195</v>
+        <v>348178</v>
       </c>
       <c r="R3" t="n">
-        <v>6519676</v>
+        <v>6519779</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,24 +920,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskog med en hel del gran men även tall på frisk- frisk-fuktig och fuktig mark. Förekomst av stående död ved.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1082,6 +1082,574 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121854116</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svaltorpsmossarna, Grönhult, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>348128</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6519755</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre hackspår (födosökspår) i en helt död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121854022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svaltorpsmossarna, Grönhult, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>348130</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6519757</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hackspår (födosökspår) i en helt död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121857836</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svaltorpsmossarna, Grönhult, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>348245</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6519706</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hackspår i en döende något smalare gran.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121857009</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svaltorpsmossarna, Grönhult, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>348203</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6519731</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Större hackspår i basen av en stående död delvis avbarkad tall.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53915-2024 artfynd.xlsx
+++ b/artfynd/A 53915-2024 artfynd.xlsx
@@ -940,7 +940,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121857836</v>
+        <v>121857009</v>
       </c>
       <c r="B4" t="n">
         <v>57390</v>
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>348245</v>
+        <v>348203</v>
       </c>
       <c r="R4" t="n">
-        <v>6519706</v>
+        <v>6519731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hackspår i en döende något smalare gran.</t>
+          <t>Större hackspår i basen av en stående död delvis avbarkad tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,22 +1049,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121857009</v>
+        <v>121857836</v>
       </c>
       <c r="B5" t="n">
         <v>57390</v>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>348203</v>
+        <v>348245</v>
       </c>
       <c r="R5" t="n">
-        <v>6519731</v>
+        <v>6519706</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Större hackspår i basen av en stående död delvis avbarkad tall.</t>
+          <t>Hackspår i en döende något smalare gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 53915-2024 artfynd.xlsx
+++ b/artfynd/A 53915-2024 artfynd.xlsx
@@ -1224,7 +1224,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121854116</v>
+        <v>121854022</v>
       </c>
       <c r="B6" t="n">
         <v>57390</v>
@@ -1260,7 +1260,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>348128</v>
+        <v>348130</v>
       </c>
       <c r="R6" t="n">
-        <v>6519755</v>
+        <v>6519757</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre hackspår (födosökspår) i en helt död gran med full längd.</t>
+          <t>Färska hackspår (födosökspår) i en helt död gran med full längd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1366,7 +1366,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121854022</v>
+        <v>121854116</v>
       </c>
       <c r="B7" t="n">
         <v>57390</v>
@@ -1402,7 +1402,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>348130</v>
+        <v>348128</v>
       </c>
       <c r="R7" t="n">
-        <v>6519757</v>
+        <v>6519755</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hackspår (födosökspår) i en helt död gran med full längd.</t>
+          <t>Äldre hackspår (födosökspår) i en helt död gran med full längd.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 53915-2024 artfynd.xlsx
+++ b/artfynd/A 53915-2024 artfynd.xlsx
@@ -1511,7 +1511,7 @@
         <v>121795069</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 53915-2024 artfynd.xlsx
+++ b/artfynd/A 53915-2024 artfynd.xlsx
@@ -1526,11 +1526,6 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1620,11 +1615,6 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Med stor andel gran.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
